--- a/Excel/Book2.xlsx
+++ b/Excel/Book2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\j-l-data-science-data-analytics\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B32DAED-A2DE-4760-9308-C16A49CCB248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{979C11CE-BAD5-4ED2-9D5B-001E049A1C27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="29">
   <si>
     <t>Grade Book</t>
   </si>
@@ -110,6 +110,18 @@
   <si>
     <t>Points Possible</t>
   </si>
+  <si>
+    <t>Fired Employee?</t>
+  </si>
+  <si>
+    <t>MAX</t>
+  </si>
+  <si>
+    <t>MIN</t>
+  </si>
+  <si>
+    <t>AVERAGE</t>
+  </si>
 </sst>
 </file>
 
@@ -152,18 +164,110 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment textRotation="90"/>
+      <alignment textRotation="45"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="9">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -174,6 +278,3181 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:effectLst/>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Safety Test</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:gradFill>
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent1"/>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="84000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="1"/>
+            </a:gradFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="76200" dir="18900000" sy="23000" kx="-1200000" algn="bl" rotWithShape="0">
+                <a:prstClr val="black">
+                  <a:alpha val="20000"/>
+                </a:prstClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="inEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="dk1">
+                          <a:lumMod val="50000"/>
+                          <a:lumOff val="50000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$4:$A$20</c:f>
+              <c:strCache>
+                <c:ptCount val="17"/>
+                <c:pt idx="0">
+                  <c:v>Jafar Loka-01</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Jafar Loka-02</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Jafar Loka-03</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Jafar Loka-04</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Jafar Loka-05</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Jafar Loka-06</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Jafar Loka-07</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Jafar Loka-08</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Jafar Loka-09</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Jafar Loka-10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Jafar Loka-11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Jafar Loka-12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Jafar Loka-13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Jafar Loka-14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Jafar Loka-15</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>Jafar Loka-16</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>Jafar Loka-17</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$4:$C$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="17"/>
+                <c:pt idx="0">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>7</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-56A0-4545-B495-9A5DD05F204C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="inEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="41"/>
+        <c:axId val="1348457232"/>
+        <c:axId val="1348451952"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1348457232"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:effectLst/>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1348451952"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1348451952"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1348457232"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:schemeClr val="lt1"/>
+        </a:gs>
+        <a:gs pos="68000">
+          <a:schemeClr val="lt1">
+            <a:lumMod val="85000"/>
+          </a:schemeClr>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:schemeClr val="lt1"/>
+        </a:gs>
+      </a:gsLst>
+      <a:lin ang="5400000" scaled="1"/>
+      <a:tileRect/>
+    </a:gradFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="95000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:effectLst>
+                  <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                    <a:prstClr val="black">
+                      <a:alpha val="40000"/>
+                    </a:prstClr>
+                  </a:outerShdw>
+                </a:effectLst>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Company Philosophy Test</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:effectLst>
+                <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="40000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="103000"/>
+                    <a:lumMod val="102000"/>
+                    <a:tint val="94000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="110000"/>
+                    <a:lumMod val="100000"/>
+                    <a:shade val="100000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="99000"/>
+                    <a:satMod val="120000"/>
+                    <a:shade val="78000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$B$4:$B$20</c:f>
+              <c:strCache>
+                <c:ptCount val="17"/>
+                <c:pt idx="0">
+                  <c:v>Jafar Loka-01</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Jafar Loka-02</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Jafar Loka-03</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Jafar Loka-04</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Jafar Loka-05</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Jafar Loka-06</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Jafar Loka-07</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Jafar Loka-08</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Jafar Loka-09</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Jafar Loka-10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Jafar Loka-11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Jafar Loka-12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Jafar Loka-13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Jafar Loka-14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Jafar Loka-15</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>Jafar Loka-16</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>Jafar Loka-17</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$4:$D$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="17"/>
+                <c:pt idx="0">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>15</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-D984-46A7-ACB7-382692D4E3DE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="100"/>
+        <c:overlap val="-24"/>
+        <c:axId val="1329460560"/>
+        <c:axId val="1329461040"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1329460560"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:lumMod val="95000"/>
+                <a:alpha val="54000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1329461040"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1329461040"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                  <a:alpha val="10000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1329460560"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="85000"/>
+            <a:lumOff val="15000"/>
+          </a:schemeClr>
+        </a:gs>
+      </a:gsLst>
+      <a:path path="circle">
+        <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+      </a:path>
+      <a:tileRect/>
+    </a:gradFill>
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="50" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Financial Skills Test</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="50" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:gradFill flip="none" rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent1"/>
+                </a:gs>
+                <a:gs pos="75000">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="60000"/>
+                    <a:lumOff val="40000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="51000">
+                  <a:schemeClr val="accent1">
+                    <a:alpha val="75000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                    <a:alpha val="15000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$B$4:$B$20</c:f>
+              <c:strCache>
+                <c:ptCount val="17"/>
+                <c:pt idx="0">
+                  <c:v>Jafar Loka-01</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Jafar Loka-02</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Jafar Loka-03</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Jafar Loka-04</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Jafar Loka-05</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Jafar Loka-06</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Jafar Loka-07</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Jafar Loka-08</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Jafar Loka-09</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Jafar Loka-10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Jafar Loka-11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Jafar Loka-12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Jafar Loka-13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Jafar Loka-14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Jafar Loka-15</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>Jafar Loka-16</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>Jafar Loka-17</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$E$4:$E$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="17"/>
+                <c:pt idx="0">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>96</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>69</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>95</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>57</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>92</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>92</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>96</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>95</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>82</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>77</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>96</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>57</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>69</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-7873-4400-BA97-9AC90627EC78}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="355"/>
+        <c:overlap val="-70"/>
+        <c:axId val="1622384000"/>
+        <c:axId val="1622404160"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1622384000"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1622404160"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1622404160"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:gradFill>
+                <a:gsLst>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="5000"/>
+                      <a:lumOff val="95000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="0">
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="25000"/>
+                      <a:lumOff val="75000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1622384000"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="204">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200">
+      <a:effectLst/>
+    </cs:defRPr>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="lt1"/>
+          </a:gs>
+          <a:gs pos="68000">
+            <a:schemeClr val="lt1">
+              <a:lumMod val="85000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="lt1"/>
+          </a:gs>
+        </a:gsLst>
+        <a:lin ang="5400000" scaled="1"/>
+        <a:tileRect/>
+      </a:gradFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr/>
+    <cs:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+          <a:alpha val="75000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="1000" b="1" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill>
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="phClr"/>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="phClr">
+              <a:lumMod val="84000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:lin ang="5400000" scaled="1"/>
+      </a:gradFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="76200" dir="18900000" sy="23000" kx="-1200000" algn="bl" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="20000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill>
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="phClr"/>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="phClr">
+              <a:lumMod val="84000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:lin ang="5400000" scaled="1"/>
+      </a:gradFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="76200" dir="18900000" sy="23000" kx="-1200000" algn="bl" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="20000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr"/>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="84000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="1"/>
+        </a:gradFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill>
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="phClr"/>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="phClr">
+              <a:lumMod val="84000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:lin ang="5400000" scaled="1"/>
+      </a:gradFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="76200" dir="18900000" sy="23000" kx="-1200000" algn="bl" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="20000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="35000"/>
+          <a:lumOff val="65000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr kern="1200">
+      <a:effectLst/>
+    </cs:defRPr>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="95000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="209">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="85000"/>
+              <a:lumOff val="15000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+        </a:path>
+        <a:tileRect/>
+      </a:gradFill>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="34925" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="10000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="5000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="95000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" spc="100" baseline="0">
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:defRPr>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="210">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="bg1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="50000"/>
+          <a:lumOff val="50000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="phClr"/>
+          </a:gs>
+          <a:gs pos="75000">
+            <a:schemeClr val="phClr">
+              <a:lumMod val="60000"/>
+              <a:lumOff val="40000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="51000">
+            <a:schemeClr val="phClr">
+              <a:alpha val="75000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="phClr">
+              <a:lumMod val="20000"/>
+              <a:lumOff val="80000"/>
+              <a:alpha val="15000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:lin ang="5400000" scaled="0"/>
+      </a:gradFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="phClr"/>
+          </a:gs>
+          <a:gs pos="75000">
+            <a:schemeClr val="phClr">
+              <a:lumMod val="60000"/>
+              <a:lumOff val="40000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="51000">
+            <a:schemeClr val="phClr">
+              <a:alpha val="75000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="phClr">
+              <a:lumMod val="20000"/>
+              <a:lumOff val="80000"/>
+              <a:alpha val="15000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:lin ang="5400000" scaled="0"/>
+      </a:gradFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="phClr"/>
+          </a:gs>
+          <a:gs pos="75000">
+            <a:schemeClr val="phClr">
+              <a:lumMod val="60000"/>
+              <a:lumOff val="40000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="51000">
+            <a:schemeClr val="phClr">
+              <a:alpha val="75000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="phClr">
+              <a:lumMod val="20000"/>
+              <a:lumOff val="80000"/>
+              <a:alpha val="15000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:lin ang="5400000" scaled="0"/>
+      </a:gradFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:shade val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="tx1">
+                <a:lumMod val="5000"/>
+                <a:lumOff val="95000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="tx1">
+                <a:lumMod val="5000"/>
+                <a:lumOff val="95000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+        <a:headEnd type="none" w="sm" len="sm"/>
+        <a:tailEnd type="none" w="sm" len="sm"/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1800" b="1" kern="1200" cap="all" spc="50" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>116417</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>141816</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>508000</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>148165</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F5D91384-32F3-C45F-7D92-2F250CE2C30C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>105833</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>529165</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{87334B3F-EA91-F931-6680-1CC3805CF94F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>116415</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>57151</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>529165</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>133351</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{33CF0689-CC64-214F-50DA-9381C9C7EA4B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -439,47 +3718,57 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="7.5703125" customWidth="1"/>
-    <col min="4" max="4" width="9.28515625" customWidth="1"/>
-    <col min="5" max="5" width="8.28515625" customWidth="1"/>
-    <col min="6" max="6" width="8.42578125" customWidth="1"/>
-    <col min="8" max="8" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="132" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:13" ht="132" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="G1" s="2"/>
+      <c r="H1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>23</v>
       </c>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>24</v>
       </c>
@@ -496,7 +3785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -504,7 +3793,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -512,27 +3801,43 @@
         <v>3</v>
       </c>
       <c r="C4">
-        <f ca="1">RANDBETWEEN(1, 10)</f>
-        <v>3</v>
+        <f ca="1">RANDBETWEEN(5, 10)</f>
+        <v>6</v>
       </c>
       <c r="D4">
-        <f ca="1">RANDBETWEEN(1, 20)</f>
-        <v>3</v>
+        <f ca="1">RANDBETWEEN(10, 20)</f>
+        <v>11</v>
       </c>
       <c r="E4">
-        <f ca="1">RANDBETWEEN(1, 100)</f>
-        <v>17</v>
+        <f ca="1">RANDBETWEEN(50, 100)</f>
+        <v>75</v>
       </c>
       <c r="F4">
         <f ca="1">RANDBETWEEN(0, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="H4" s="1">
+        <f ca="1">C4/C$2</f>
+        <v>0.6</v>
+      </c>
+      <c r="I4" s="1">
+        <f ca="1">D4/D$2</f>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="J4" s="1">
+        <f t="shared" ref="J4:K19" ca="1" si="0">E4/E$2</f>
+        <v>0.75</v>
+      </c>
+      <c r="K4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M4" s="1" t="b">
+        <f ca="1">OR(H4&lt;0.5, I4&lt;0.5, J4&lt;0.5, K4&lt;0.5)</f>
         <v>0</v>
       </c>
-      <c r="H4" s="2">
-        <f ca="1">C4/C$2</f>
-        <v>0.3</v>
-      </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -540,27 +3845,43 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <f t="shared" ref="C5:C20" ca="1" si="0">RANDBETWEEN(1, 10)</f>
-        <v>3</v>
+        <f t="shared" ref="C5:C20" ca="1" si="1">RANDBETWEEN(5, 10)</f>
+        <v>5</v>
       </c>
       <c r="D5">
-        <f t="shared" ref="D5:D20" ca="1" si="1">RANDBETWEEN(1, 20)</f>
-        <v>3</v>
+        <f t="shared" ref="D5:D20" ca="1" si="2">RANDBETWEEN(10, 20)</f>
+        <v>14</v>
       </c>
       <c r="E5">
-        <f t="shared" ref="E5:E20" ca="1" si="2">RANDBETWEEN(1, 100)</f>
-        <v>2</v>
+        <f t="shared" ref="E5:E20" ca="1" si="3">RANDBETWEEN(50, 100)</f>
+        <v>96</v>
       </c>
       <c r="F5">
-        <f t="shared" ref="F5:F20" ca="1" si="3">RANDBETWEEN(0, 1)</f>
+        <f t="shared" ref="F5:F20" ca="1" si="4">RANDBETWEEN(0, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="H5" s="1">
+        <f t="shared" ref="H5:I20" ca="1" si="5">C5/C$2</f>
+        <v>0.5</v>
+      </c>
+      <c r="I5" s="1">
+        <f t="shared" ca="1" si="5"/>
+        <v>0.7</v>
+      </c>
+      <c r="J5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.96</v>
+      </c>
+      <c r="K5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M5" s="1" t="b">
+        <f t="shared" ref="M5:M20" ca="1" si="6">OR(H5&lt;0.5, I5&lt;0.5, J5&lt;0.5, K5&lt;0.5)</f>
         <v>0</v>
       </c>
-      <c r="H5" s="2">
-        <f t="shared" ref="H5:H20" ca="1" si="4">C5/C$2</f>
-        <v>0.3</v>
-      </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -568,27 +3889,43 @@
         <v>5</v>
       </c>
       <c r="C6">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="D6">
         <f t="shared" ca="1" si="1"/>
         <v>10</v>
       </c>
+      <c r="D6">
+        <f t="shared" ca="1" si="2"/>
+        <v>17</v>
+      </c>
       <c r="E6">
-        <f t="shared" ca="1" si="2"/>
-        <v>71</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>69</v>
       </c>
       <c r="F6">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
+        <f t="shared" ca="1" si="5"/>
         <v>1</v>
       </c>
-      <c r="H6" s="2">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.2</v>
+      <c r="I6" s="1">
+        <f t="shared" ca="1" si="5"/>
+        <v>0.85</v>
+      </c>
+      <c r="J6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.69</v>
+      </c>
+      <c r="K6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M6" s="1" t="b">
+        <f t="shared" ca="1" si="6"/>
+        <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -596,27 +3933,43 @@
         <v>6</v>
       </c>
       <c r="C7">
+        <f t="shared" ca="1" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="D7">
+        <f t="shared" ca="1" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="E7">
+        <f t="shared" ca="1" si="3"/>
+        <v>95</v>
+      </c>
+      <c r="F7">
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
+        <f t="shared" ca="1" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="I7" s="1">
+        <f t="shared" ca="1" si="5"/>
+        <v>0.75</v>
+      </c>
+      <c r="J7" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="D7">
-        <f t="shared" ca="1" si="1"/>
-        <v>18</v>
-      </c>
-      <c r="E7">
-        <f t="shared" ca="1" si="2"/>
-        <v>53</v>
-      </c>
-      <c r="F7">
-        <f t="shared" ca="1" si="3"/>
+        <v>0.95</v>
+      </c>
+      <c r="K7" s="1">
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
-      <c r="H7" s="2">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.7</v>
+      <c r="M7" s="1" t="b">
+        <f t="shared" ca="1" si="6"/>
+        <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -624,139 +3977,219 @@
         <v>7</v>
       </c>
       <c r="C8">
+        <f t="shared" ca="1" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="D8">
+        <f t="shared" ca="1" si="2"/>
+        <v>11</v>
+      </c>
+      <c r="E8">
+        <f t="shared" ca="1" si="3"/>
+        <v>57</v>
+      </c>
+      <c r="F8">
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="H8" s="1">
+        <f t="shared" ca="1" si="5"/>
+        <v>0.7</v>
+      </c>
+      <c r="I8" s="1">
+        <f t="shared" ca="1" si="5"/>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="J8" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="D8">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="K8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M8" s="1" t="b">
+        <f t="shared" ca="1" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9">
+        <f t="shared" ca="1" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="D9">
+        <f t="shared" ca="1" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="E9">
+        <f t="shared" ca="1" si="3"/>
+        <v>70</v>
+      </c>
+      <c r="F9">
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="H9" s="1">
+        <f t="shared" ca="1" si="5"/>
+        <v>0.8</v>
+      </c>
+      <c r="I9" s="1">
+        <f t="shared" ca="1" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="J9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.7</v>
+      </c>
+      <c r="K9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M9" s="1" t="b">
+        <f t="shared" ca="1" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10">
+        <f t="shared" ca="1" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="D10">
+        <f t="shared" ca="1" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="E10">
+        <f t="shared" ca="1" si="3"/>
+        <v>92</v>
+      </c>
+      <c r="F10">
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H10" s="1">
+        <f t="shared" ca="1" si="5"/>
+        <v>0.9</v>
+      </c>
+      <c r="I10" s="1">
+        <f t="shared" ca="1" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="J10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.92</v>
+      </c>
+      <c r="K10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M10" s="1" t="b">
+        <f t="shared" ca="1" si="6"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11">
+        <f t="shared" ca="1" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="D11">
+        <f t="shared" ca="1" si="2"/>
+        <v>11</v>
+      </c>
+      <c r="E11">
+        <f t="shared" ca="1" si="3"/>
+        <v>50</v>
+      </c>
+      <c r="F11">
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H11" s="1">
+        <f t="shared" ca="1" si="5"/>
+        <v>0.9</v>
+      </c>
+      <c r="I11" s="1">
+        <f t="shared" ca="1" si="5"/>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="J11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="K11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M11" s="1" t="b">
+        <f t="shared" ca="1" si="6"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12">
         <f t="shared" ca="1" si="1"/>
         <v>10</v>
       </c>
-      <c r="E8">
+      <c r="D12">
         <f t="shared" ca="1" si="2"/>
-        <v>98</v>
-      </c>
-      <c r="F8">
+        <v>16</v>
+      </c>
+      <c r="E12">
         <f t="shared" ca="1" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="H8" s="2">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="D9">
-        <f t="shared" ca="1" si="1"/>
-        <v>16</v>
-      </c>
-      <c r="E9">
-        <f t="shared" ca="1" si="2"/>
-        <v>49</v>
-      </c>
-      <c r="F9">
-        <f t="shared" ca="1" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H9" s="2">
+        <v>92</v>
+      </c>
+      <c r="F12">
         <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
+      <c r="H12" s="1">
+        <f t="shared" ca="1" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="I12" s="1">
+        <f t="shared" ca="1" si="5"/>
+        <v>0.8</v>
+      </c>
+      <c r="J12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.92</v>
+      </c>
+      <c r="K12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M12" s="1" t="b">
+        <f t="shared" ca="1" si="6"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10">
-        <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="D10">
-        <f t="shared" ca="1" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="E10">
-        <f t="shared" ca="1" si="2"/>
-        <v>51</v>
-      </c>
-      <c r="F10">
-        <f t="shared" ca="1" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="H10" s="2">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="D11">
-        <f t="shared" ca="1" si="1"/>
-        <v>11</v>
-      </c>
-      <c r="E11">
-        <f t="shared" ca="1" si="2"/>
-        <v>8</v>
-      </c>
-      <c r="F11">
-        <f t="shared" ca="1" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H11" s="2">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="D12">
-        <f t="shared" ca="1" si="1"/>
-        <v>18</v>
-      </c>
-      <c r="E12">
-        <f t="shared" ca="1" si="2"/>
-        <v>37</v>
-      </c>
-      <c r="F12">
-        <f t="shared" ca="1" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="H12" s="2">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -764,27 +4197,43 @@
         <v>12</v>
       </c>
       <c r="C13">
+        <f t="shared" ca="1" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="D13">
+        <f t="shared" ca="1" si="2"/>
+        <v>19</v>
+      </c>
+      <c r="E13">
+        <f t="shared" ca="1" si="3"/>
+        <v>60</v>
+      </c>
+      <c r="F13">
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="H13" s="1">
+        <f t="shared" ca="1" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="I13" s="1">
+        <f t="shared" ca="1" si="5"/>
+        <v>0.95</v>
+      </c>
+      <c r="J13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="D13">
-        <f t="shared" ca="1" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="E13">
-        <f t="shared" ca="1" si="2"/>
-        <v>38</v>
-      </c>
-      <c r="F13">
-        <f t="shared" ca="1" si="3"/>
+        <v>0.6</v>
+      </c>
+      <c r="K13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M13" s="1" t="b">
+        <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
-      <c r="H13" s="2">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.8</v>
-      </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -792,195 +4241,472 @@
         <v>13</v>
       </c>
       <c r="C14">
+        <f t="shared" ca="1" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="D14">
+        <f t="shared" ca="1" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="E14">
+        <f t="shared" ca="1" si="3"/>
+        <v>96</v>
+      </c>
+      <c r="F14">
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
+        <f t="shared" ca="1" si="5"/>
+        <v>0.7</v>
+      </c>
+      <c r="I14" s="1">
+        <f t="shared" ca="1" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="J14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="D14">
+        <v>0.96</v>
+      </c>
+      <c r="K14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M14" s="1" t="b">
+        <f t="shared" ca="1" si="6"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15">
         <f t="shared" ca="1" si="1"/>
-        <v>13</v>
-      </c>
-      <c r="E14">
+        <v>9</v>
+      </c>
+      <c r="D15">
         <f t="shared" ca="1" si="2"/>
-        <v>88</v>
-      </c>
-      <c r="F14">
+        <v>17</v>
+      </c>
+      <c r="E15">
         <f t="shared" ca="1" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="H14" s="2">
+        <v>95</v>
+      </c>
+      <c r="F15">
         <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
+      <c r="H15" s="1">
+        <f t="shared" ca="1" si="5"/>
+        <v>0.9</v>
+      </c>
+      <c r="I15" s="1">
+        <f t="shared" ca="1" si="5"/>
+        <v>0.85</v>
+      </c>
+      <c r="J15" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.95</v>
+      </c>
+      <c r="K15" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M15" s="1" t="b">
+        <f t="shared" ca="1" si="6"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16">
+        <f t="shared" ca="1" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="D16">
+        <f t="shared" ca="1" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="E16">
+        <f t="shared" ca="1" si="3"/>
+        <v>82</v>
+      </c>
+      <c r="F16">
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H16" s="1">
+        <f t="shared" ca="1" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="I16" s="1">
+        <f t="shared" ca="1" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="J16" s="1">
         <f t="shared" ca="1" si="0"/>
+        <v>0.82</v>
+      </c>
+      <c r="K16" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M16" s="1" t="b">
+        <f t="shared" ca="1" si="6"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17">
+        <f t="shared" ca="1" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="D17">
+        <f t="shared" ca="1" si="2"/>
         <v>10</v>
       </c>
-      <c r="D15">
+      <c r="E17">
+        <f t="shared" ca="1" si="3"/>
+        <v>77</v>
+      </c>
+      <c r="F17">
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H17" s="1">
+        <f t="shared" ca="1" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="I17" s="1">
+        <f t="shared" ca="1" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="J17" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.77</v>
+      </c>
+      <c r="K17" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M17" s="1" t="b">
+        <f t="shared" ca="1" si="6"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18">
         <f t="shared" ca="1" si="1"/>
-        <v>18</v>
-      </c>
-      <c r="E15">
+        <v>8</v>
+      </c>
+      <c r="D18">
         <f t="shared" ca="1" si="2"/>
-        <v>23</v>
-      </c>
-      <c r="F15">
+        <v>15</v>
+      </c>
+      <c r="E18">
         <f t="shared" ca="1" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="H15" s="2">
+        <v>96</v>
+      </c>
+      <c r="F18">
         <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
+      <c r="H18" s="1">
+        <f t="shared" ca="1" si="5"/>
+        <v>0.8</v>
+      </c>
+      <c r="I18" s="1">
+        <f t="shared" ca="1" si="5"/>
+        <v>0.75</v>
+      </c>
+      <c r="J18" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.96</v>
+      </c>
+      <c r="K18" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M18" s="1" t="b">
+        <f t="shared" ca="1" si="6"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16">
-        <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="D16">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="E16">
+        <v>7</v>
+      </c>
+      <c r="D19">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="F16">
+        <v>16</v>
+      </c>
+      <c r="E19">
         <f t="shared" ca="1" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H16" s="2">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="D17">
-        <f t="shared" ca="1" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="E17">
-        <f t="shared" ca="1" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="F17">
-        <f t="shared" ca="1" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H17" s="2">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B18" t="s">
-        <v>17</v>
-      </c>
-      <c r="C18">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="D18">
-        <f t="shared" ca="1" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="E18">
-        <f t="shared" ca="1" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="F18">
-        <f t="shared" ca="1" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="H18" s="2">
+        <v>57</v>
+      </c>
+      <c r="F19">
         <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
+      <c r="H19" s="1">
+        <f t="shared" ca="1" si="5"/>
+        <v>0.7</v>
+      </c>
+      <c r="I19" s="1">
+        <f t="shared" ca="1" si="5"/>
+        <v>0.8</v>
+      </c>
+      <c r="J19" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="K19" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M19" s="1" t="b">
+        <f t="shared" ca="1" si="6"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C19">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="D19">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="E19">
+        <v>7</v>
+      </c>
+      <c r="D20">
         <f t="shared" ca="1" si="2"/>
-        <v>63</v>
-      </c>
-      <c r="F19">
+        <v>15</v>
+      </c>
+      <c r="E20">
         <f t="shared" ca="1" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="H19" s="2">
+        <v>69</v>
+      </c>
+      <c r="F20">
         <f t="shared" ca="1" si="4"/>
         <v>1</v>
       </c>
+      <c r="H20" s="1">
+        <f t="shared" ca="1" si="5"/>
+        <v>0.7</v>
+      </c>
+      <c r="I20" s="1">
+        <f t="shared" ca="1" si="5"/>
+        <v>0.75</v>
+      </c>
+      <c r="J20" s="1">
+        <f t="shared" ref="J20" ca="1" si="7">E20/E$2</f>
+        <v>0.69</v>
+      </c>
+      <c r="K20" s="1">
+        <f t="shared" ref="K20" ca="1" si="8">F20/F$2</f>
+        <v>1</v>
+      </c>
+      <c r="M20" s="1" t="b">
+        <f t="shared" ca="1" si="6"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>19</v>
-      </c>
-      <c r="B20" t="s">
-        <v>19</v>
-      </c>
-      <c r="C20">
-        <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="D20">
-        <f t="shared" ca="1" si="1"/>
-        <v>14</v>
-      </c>
-      <c r="E20">
-        <f t="shared" ca="1" si="2"/>
-        <v>36</v>
-      </c>
-      <c r="F20">
-        <f t="shared" ca="1" si="3"/>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22">
+        <f ca="1">MAX(C4:C20)</f>
+        <v>10</v>
+      </c>
+      <c r="D22">
+        <f t="shared" ref="D22:F22" ca="1" si="9">MAX(D4:D20)</f>
+        <v>20</v>
+      </c>
+      <c r="E22">
+        <f t="shared" ca="1" si="9"/>
+        <v>96</v>
+      </c>
+      <c r="F22">
+        <f t="shared" ref="F22" ca="1" si="10">MAX(F4:F20)</f>
+        <v>1</v>
+      </c>
+      <c r="H22" s="1">
+        <f ca="1">MAX(H4:H20)</f>
+        <v>1</v>
+      </c>
+      <c r="I22" s="1">
+        <f t="shared" ref="I22:K22" ca="1" si="11">MAX(I4:I20)</f>
+        <v>1</v>
+      </c>
+      <c r="J22" s="1">
+        <f t="shared" ca="1" si="11"/>
+        <v>0.96</v>
+      </c>
+      <c r="K22" s="1">
+        <f t="shared" ca="1" si="11"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23">
+        <f ca="1">MIN(C4:C20)</f>
+        <v>5</v>
+      </c>
+      <c r="D23">
+        <f t="shared" ref="D23:F23" ca="1" si="12">MIN(D4:D20)</f>
+        <v>10</v>
+      </c>
+      <c r="E23">
+        <f t="shared" ca="1" si="12"/>
+        <v>50</v>
+      </c>
+      <c r="F23">
+        <f t="shared" ref="F23" ca="1" si="13">MIN(F4:F20)</f>
         <v>0</v>
       </c>
-      <c r="H20" s="2">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.6</v>
+      <c r="H23" s="1">
+        <f ca="1">MIN(H4:H20)</f>
+        <v>0.5</v>
+      </c>
+      <c r="I23" s="1">
+        <f t="shared" ref="I23:K23" ca="1" si="14">MIN(I4:I20)</f>
+        <v>0.5</v>
+      </c>
+      <c r="J23" s="1">
+        <f t="shared" ca="1" si="14"/>
+        <v>0.5</v>
+      </c>
+      <c r="K23" s="1">
+        <f t="shared" ca="1" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>28</v>
+      </c>
+      <c r="C24" s="3">
+        <f ca="1">AVERAGE(C4:C21)</f>
+        <v>7.7647058823529411</v>
+      </c>
+      <c r="D24" s="3">
+        <f t="shared" ref="D24:F24" ca="1" si="15">AVERAGE(D4:D21)</f>
+        <v>14.529411764705882</v>
+      </c>
+      <c r="E24" s="3">
+        <f t="shared" ca="1" si="15"/>
+        <v>78.117647058823536</v>
+      </c>
+      <c r="F24" s="3">
+        <f t="shared" ref="F24" ca="1" si="16">AVERAGE(F4:F21)</f>
+        <v>0.58823529411764708</v>
+      </c>
+      <c r="H24" s="1">
+        <f ca="1">AVERAGE(H4:H21)</f>
+        <v>0.77647058823529402</v>
+      </c>
+      <c r="I24" s="1">
+        <f t="shared" ref="I24:K24" ca="1" si="17">AVERAGE(I4:I21)</f>
+        <v>0.7264705882352942</v>
+      </c>
+      <c r="J24" s="1">
+        <f t="shared" ca="1" si="17"/>
+        <v>0.78117647058823525</v>
+      </c>
+      <c r="K24" s="1">
+        <f t="shared" ca="1" si="17"/>
+        <v>0.58823529411764708</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="C4:C20">
+    <cfRule type="iconSet" priority="7">
+      <iconSet iconSet="4TrafficLights">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="25"/>
+        <cfvo type="percent" val="50"/>
+        <cfvo type="percent" val="75"/>
+      </iconSet>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4:D20">
+    <cfRule type="iconSet" priority="6">
+      <iconSet iconSet="4TrafficLights">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="25"/>
+        <cfvo type="percent" val="50"/>
+        <cfvo type="percent" val="75"/>
+      </iconSet>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E4:E20">
+    <cfRule type="iconSet" priority="5">
+      <iconSet iconSet="4TrafficLights">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="25"/>
+        <cfvo type="percent" val="50"/>
+        <cfvo type="percent" val="75"/>
+      </iconSet>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F4:F20">
+    <cfRule type="iconSet" priority="4">
+      <iconSet iconSet="4TrafficLights">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="25"/>
+        <cfvo type="percent" val="50"/>
+        <cfvo type="percent" val="75"/>
+      </iconSet>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4:K20 M4:M20">
+    <cfRule type="cellIs" dxfId="7" priority="3" operator="lessThan">
+      <formula>0.5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M4:M20">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
+      <formula>TRUE</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+      <formula>FALSE</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Excel/Book2.xlsx
+++ b/Excel/Book2.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\j-l-data-science-data-analytics\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{979C11CE-BAD5-4ED2-9D5B-001E049A1C27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7595D284-73C5-4278-9572-DDF04F7D8383}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="42">
   <si>
     <t>Grade Book</t>
   </si>
@@ -122,12 +123,51 @@
   <si>
     <t>AVERAGE</t>
   </si>
+  <si>
+    <t>Career Decision Time</t>
+  </si>
+  <si>
+    <t>Job</t>
+  </si>
+  <si>
+    <t>Jafar-Loka-01</t>
+  </si>
+  <si>
+    <t>Jafar-Loka-02</t>
+  </si>
+  <si>
+    <t>Jafar-Loka-03</t>
+  </si>
+  <si>
+    <t>Jafar-Loka-04</t>
+  </si>
+  <si>
+    <t>Jafar-Loka-05</t>
+  </si>
+  <si>
+    <t>Pay</t>
+  </si>
+  <si>
+    <t>Job Market</t>
+  </si>
+  <si>
+    <t>Enjoyment</t>
+  </si>
+  <si>
+    <t>My Talent</t>
+  </si>
+  <si>
+    <t>Schooling</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -142,13 +182,74 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="9" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFABF84"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -164,39 +265,32 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment textRotation="45"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="9">
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -237,38 +331,13 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFABF84"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -507,52 +576,52 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="17"/>
                 <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>6</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>7</c:v>
                 </c:pt>
-                <c:pt idx="5">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>9</c:v>
                 </c:pt>
-                <c:pt idx="7">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>10</c:v>
-                </c:pt>
                 <c:pt idx="9">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>5</c:v>
                 </c:pt>
-                <c:pt idx="10">
-                  <c:v>7</c:v>
-                </c:pt>
                 <c:pt idx="11">
-                  <c:v>9</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>5</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>7</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>7</c:v>
@@ -902,55 +971,55 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="17"/>
                 <c:pt idx="0">
-                  <c:v>11</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>14</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>17</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>15</c:v>
+                  <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>11</c:v>
                 </c:pt>
-                <c:pt idx="5">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="11">
                   <c:v>19</c:v>
                 </c:pt>
-                <c:pt idx="10">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>17</c:v>
-                </c:pt>
                 <c:pt idx="12">
-                  <c:v>20</c:v>
+                  <c:v>18</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>10</c:v>
+                  <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>15</c:v>
+                  <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>15</c:v>
+                  <c:v>19</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1320,55 +1389,55 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="17"/>
                 <c:pt idx="0">
-                  <c:v>75</c:v>
+                  <c:v>80</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>96</c:v>
+                  <c:v>74</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>69</c:v>
+                  <c:v>54</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>95</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>57</c:v>
+                  <c:v>93</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>70</c:v>
+                  <c:v>53</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>92</c:v>
+                  <c:v>59</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>50</c:v>
+                  <c:v>56</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>92</c:v>
+                  <c:v>80</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>60</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>96</c:v>
+                  <c:v>69</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>97</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>95</c:v>
                 </c:pt>
-                <c:pt idx="12">
-                  <c:v>82</c:v>
-                </c:pt>
                 <c:pt idx="13">
-                  <c:v>77</c:v>
+                  <c:v>83</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>96</c:v>
+                  <c:v>84</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>57</c:v>
+                  <c:v>64</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>69</c:v>
+                  <c:v>89</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3718,6 +3787,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:M24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3802,39 +3874,39 @@
       </c>
       <c r="C4">
         <f ca="1">RANDBETWEEN(5, 10)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D4">
         <f ca="1">RANDBETWEEN(10, 20)</f>
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E4">
         <f ca="1">RANDBETWEEN(50, 100)</f>
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F4">
         <f ca="1">RANDBETWEEN(0, 1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" s="1">
         <f ca="1">C4/C$2</f>
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="I4" s="1">
         <f ca="1">D4/D$2</f>
-        <v>0.55000000000000004</v>
+        <v>1</v>
       </c>
       <c r="J4" s="1">
         <f t="shared" ref="J4:K19" ca="1" si="0">E4/E$2</f>
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="K4" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" s="1" t="b">
         <f ca="1">OR(H4&lt;0.5, I4&lt;0.5, J4&lt;0.5, K4&lt;0.5)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
@@ -3846,15 +3918,15 @@
       </c>
       <c r="C5">
         <f t="shared" ref="C5:C20" ca="1" si="1">RANDBETWEEN(5, 10)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5">
         <f t="shared" ref="D5:D20" ca="1" si="2">RANDBETWEEN(10, 20)</f>
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E5">
         <f t="shared" ref="E5:E20" ca="1" si="3">RANDBETWEEN(50, 100)</f>
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="F5">
         <f t="shared" ref="F5:F20" ca="1" si="4">RANDBETWEEN(0, 1)</f>
@@ -3862,15 +3934,15 @@
       </c>
       <c r="H5" s="1">
         <f t="shared" ref="H5:I20" ca="1" si="5">C5/C$2</f>
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="I5" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J5" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.96</v>
+        <v>0.74</v>
       </c>
       <c r="K5" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -3890,7 +3962,7 @@
       </c>
       <c r="C6">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D6">
         <f t="shared" ca="1" si="2"/>
@@ -3898,7 +3970,7 @@
       </c>
       <c r="E6">
         <f t="shared" ca="1" si="3"/>
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F6">
         <f t="shared" ca="1" si="4"/>
@@ -3906,7 +3978,7 @@
       </c>
       <c r="H6" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I6" s="1">
         <f t="shared" ca="1" si="5"/>
@@ -3914,7 +3986,7 @@
       </c>
       <c r="J6" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.69</v>
+        <v>0.54</v>
       </c>
       <c r="K6" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -3938,7 +4010,7 @@
       </c>
       <c r="D7">
         <f t="shared" ca="1" si="2"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E7">
         <f t="shared" ca="1" si="3"/>
@@ -3954,7 +4026,7 @@
       </c>
       <c r="I7" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="J7" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -3978,39 +4050,39 @@
       </c>
       <c r="C8">
         <f t="shared" ca="1" si="1"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D8">
         <f t="shared" ca="1" si="2"/>
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E8">
         <f t="shared" ca="1" si="3"/>
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="F8">
         <f t="shared" ca="1" si="4"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="I8" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>0.55000000000000004</v>
+        <v>0.9</v>
       </c>
       <c r="J8" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.56999999999999995</v>
+        <v>0.93</v>
       </c>
       <c r="K8" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" s="1" t="b">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
@@ -4022,39 +4094,39 @@
       </c>
       <c r="C9">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9">
         <f t="shared" ca="1" si="2"/>
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E9">
         <f t="shared" ca="1" si="3"/>
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="F9">
         <f t="shared" ca="1" si="4"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="I9" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J9" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.7</v>
+        <v>0.53</v>
       </c>
       <c r="K9" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" s="1" t="b">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
@@ -4066,15 +4138,15 @@
       </c>
       <c r="C10">
         <f t="shared" ca="1" si="1"/>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D10">
         <f t="shared" ca="1" si="2"/>
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E10">
         <f t="shared" ca="1" si="3"/>
-        <v>92</v>
+        <v>59</v>
       </c>
       <c r="F10">
         <f t="shared" ca="1" si="4"/>
@@ -4082,15 +4154,15 @@
       </c>
       <c r="H10" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="I10" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J10" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.92</v>
+        <v>0.59</v>
       </c>
       <c r="K10" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -4110,39 +4182,39 @@
       </c>
       <c r="C11">
         <f t="shared" ca="1" si="1"/>
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D11">
         <f t="shared" ca="1" si="2"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E11">
         <f t="shared" ca="1" si="3"/>
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F11">
         <f t="shared" ca="1" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="I11" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>0.55000000000000004</v>
+        <v>0.65</v>
       </c>
       <c r="J11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.5</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="K11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" s="1" t="b">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
@@ -4154,15 +4226,15 @@
       </c>
       <c r="C12">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D12">
         <f t="shared" ca="1" si="2"/>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E12">
         <f t="shared" ca="1" si="3"/>
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="F12">
         <f t="shared" ca="1" si="4"/>
@@ -4170,15 +4242,15 @@
       </c>
       <c r="H12" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="I12" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J12" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.92</v>
+        <v>0.8</v>
       </c>
       <c r="K12" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -4198,11 +4270,11 @@
       </c>
       <c r="C13">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D13">
         <f t="shared" ca="1" si="2"/>
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E13">
         <f t="shared" ca="1" si="3"/>
@@ -4214,11 +4286,11 @@
       </c>
       <c r="H13" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="I13" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>0.95</v>
+        <v>0.65</v>
       </c>
       <c r="J13" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -4242,39 +4314,39 @@
       </c>
       <c r="C14">
         <f t="shared" ca="1" si="1"/>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D14">
         <f t="shared" ca="1" si="2"/>
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E14">
         <f t="shared" ca="1" si="3"/>
-        <v>96</v>
+        <v>69</v>
       </c>
       <c r="F14">
         <f t="shared" ca="1" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="I14" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>1</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="J14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.96</v>
+        <v>0.69</v>
       </c>
       <c r="K14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" s="1" t="b">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
@@ -4286,39 +4358,39 @@
       </c>
       <c r="C15">
         <f t="shared" ca="1" si="1"/>
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D15">
         <f t="shared" ca="1" si="2"/>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E15">
         <f t="shared" ca="1" si="3"/>
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F15">
         <f t="shared" ca="1" si="4"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="I15" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="J15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="K15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" s="1" t="b">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
@@ -4334,11 +4406,11 @@
       </c>
       <c r="D16">
         <f t="shared" ca="1" si="2"/>
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E16">
         <f t="shared" ca="1" si="3"/>
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="F16">
         <f t="shared" ca="1" si="4"/>
@@ -4350,11 +4422,11 @@
       </c>
       <c r="I16" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.82</v>
+        <v>0.95</v>
       </c>
       <c r="K16" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -4374,39 +4446,39 @@
       </c>
       <c r="C17">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D17">
         <f t="shared" ca="1" si="2"/>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E17">
         <f t="shared" ca="1" si="3"/>
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="F17">
         <f t="shared" ca="1" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="I17" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.77</v>
+        <v>0.83</v>
       </c>
       <c r="K17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" s="1" t="b">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
@@ -4422,15 +4494,15 @@
       </c>
       <c r="D18">
         <f t="shared" ca="1" si="2"/>
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E18">
         <f t="shared" ca="1" si="3"/>
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="F18">
         <f t="shared" ca="1" si="4"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H18" s="1">
         <f t="shared" ca="1" si="5"/>
@@ -4438,19 +4510,19 @@
       </c>
       <c r="I18" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="J18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.96</v>
+        <v>0.84</v>
       </c>
       <c r="K18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" s="1" t="b">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
@@ -4462,7 +4534,7 @@
       </c>
       <c r="C19">
         <f t="shared" ca="1" si="1"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D19">
         <f t="shared" ca="1" si="2"/>
@@ -4470,15 +4542,15 @@
       </c>
       <c r="E19">
         <f t="shared" ca="1" si="3"/>
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="F19">
         <f t="shared" ca="1" si="4"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="I19" s="1">
         <f t="shared" ca="1" si="5"/>
@@ -4486,15 +4558,15 @@
       </c>
       <c r="J19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.56999999999999995</v>
+        <v>0.64</v>
       </c>
       <c r="K19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" s="1" t="b">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
@@ -4510,11 +4582,11 @@
       </c>
       <c r="D20">
         <f t="shared" ca="1" si="2"/>
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E20">
         <f t="shared" ca="1" si="3"/>
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="F20">
         <f t="shared" ca="1" si="4"/>
@@ -4526,11 +4598,11 @@
       </c>
       <c r="I20" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="J20" s="1">
         <f t="shared" ref="J20" ca="1" si="7">E20/E$2</f>
-        <v>0.69</v>
+        <v>0.89</v>
       </c>
       <c r="K20" s="1">
         <f t="shared" ref="K20" ca="1" si="8">F20/F$2</f>
@@ -4550,12 +4622,12 @@
         <v>10</v>
       </c>
       <c r="D22">
-        <f t="shared" ref="D22:F22" ca="1" si="9">MAX(D4:D20)</f>
+        <f t="shared" ref="D22:E22" ca="1" si="9">MAX(D4:D20)</f>
         <v>20</v>
       </c>
       <c r="E22">
         <f t="shared" ca="1" si="9"/>
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F22">
         <f t="shared" ref="F22" ca="1" si="10">MAX(F4:F20)</f>
@@ -4571,7 +4643,7 @@
       </c>
       <c r="J22" s="1">
         <f t="shared" ca="1" si="11"/>
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="K22" s="1">
         <f t="shared" ca="1" si="11"/>
@@ -4587,12 +4659,12 @@
         <v>5</v>
       </c>
       <c r="D23">
-        <f t="shared" ref="D23:F23" ca="1" si="12">MIN(D4:D20)</f>
-        <v>10</v>
+        <f t="shared" ref="D23:E23" ca="1" si="12">MIN(D4:D20)</f>
+        <v>11</v>
       </c>
       <c r="E23">
         <f t="shared" ca="1" si="12"/>
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F23">
         <f t="shared" ref="F23" ca="1" si="13">MIN(F4:F20)</f>
@@ -4604,11 +4676,11 @@
       </c>
       <c r="I23" s="1">
         <f t="shared" ref="I23:K23" ca="1" si="14">MIN(I4:I20)</f>
-        <v>0.5</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="J23" s="1">
         <f t="shared" ca="1" si="14"/>
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="K23" s="1">
         <f t="shared" ca="1" si="14"/>
@@ -4621,35 +4693,35 @@
       </c>
       <c r="C24" s="3">
         <f ca="1">AVERAGE(C4:C21)</f>
-        <v>7.7647058823529411</v>
+        <v>7</v>
       </c>
       <c r="D24" s="3">
-        <f t="shared" ref="D24:F24" ca="1" si="15">AVERAGE(D4:D21)</f>
-        <v>14.529411764705882</v>
+        <f t="shared" ref="D24:E24" ca="1" si="15">AVERAGE(D4:D21)</f>
+        <v>16</v>
       </c>
       <c r="E24" s="3">
         <f t="shared" ca="1" si="15"/>
-        <v>78.117647058823536</v>
+        <v>75.588235294117652</v>
       </c>
       <c r="F24" s="3">
         <f t="shared" ref="F24" ca="1" si="16">AVERAGE(F4:F21)</f>
-        <v>0.58823529411764708</v>
+        <v>0.41176470588235292</v>
       </c>
       <c r="H24" s="1">
         <f ca="1">AVERAGE(H4:H21)</f>
-        <v>0.77647058823529402</v>
+        <v>0.70000000000000007</v>
       </c>
       <c r="I24" s="1">
         <f t="shared" ref="I24:K24" ca="1" si="17">AVERAGE(I4:I21)</f>
-        <v>0.7264705882352942</v>
+        <v>0.79999999999999993</v>
       </c>
       <c r="J24" s="1">
         <f t="shared" ca="1" si="17"/>
-        <v>0.78117647058823525</v>
+        <v>0.75588235294117656</v>
       </c>
       <c r="K24" s="1">
         <f t="shared" ca="1" si="17"/>
-        <v>0.58823529411764708</v>
+        <v>0.41176470588235292</v>
       </c>
     </row>
   </sheetData>
@@ -4693,20 +4765,332 @@
       </iconSet>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4:K20 M4:M20">
-    <cfRule type="cellIs" dxfId="7" priority="3" operator="lessThan">
+  <conditionalFormatting sqref="M4:M20 H4:K20">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="lessThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M4:M20">
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+      <formula>FALSE</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>TRUE</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
-      <formula>FALSE</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" scale="50" orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D419627-A140-48E5-ACCB-2DB7323EEF90}">
+  <dimension ref="B1:M12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="22.28515625" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" customWidth="1"/>
+    <col min="4" max="4" width="14.140625" customWidth="1"/>
+    <col min="5" max="5" width="17.85546875" customWidth="1"/>
+    <col min="7" max="7" width="23.85546875" customWidth="1"/>
+    <col min="9" max="9" width="20" customWidth="1"/>
+    <col min="11" max="11" width="20.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B7" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="11">
+        <v>3</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" s="12">
+        <v>5</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" s="13">
+        <v>4</v>
+      </c>
+      <c r="I7" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="J7" s="14">
+        <v>3</v>
+      </c>
+      <c r="K7" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="L7" s="15">
+        <v>1</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B8" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="4">
+        <f ca="1">RANDBETWEEN(1, 5)</f>
+        <v>2</v>
+      </c>
+      <c r="D8" s="4">
+        <f ca="1">D$7*C8</f>
+        <v>6</v>
+      </c>
+      <c r="E8" s="5">
+        <f ca="1">RANDBETWEEN(1, 5)</f>
+        <v>1</v>
+      </c>
+      <c r="F8" s="5">
+        <f ca="1">F$7*E8</f>
+        <v>5</v>
+      </c>
+      <c r="G8" s="6">
+        <f ca="1">RANDBETWEEN(1, 5)</f>
+        <v>5</v>
+      </c>
+      <c r="H8" s="6">
+        <f ca="1">H$7*G8</f>
+        <v>20</v>
+      </c>
+      <c r="I8" s="7">
+        <f ca="1">RANDBETWEEN(1, 5)</f>
+        <v>3</v>
+      </c>
+      <c r="J8" s="7">
+        <f ca="1">J$7*I8</f>
+        <v>9</v>
+      </c>
+      <c r="K8" s="8">
+        <f ca="1">RANDBETWEEN(1, 5)</f>
+        <v>2</v>
+      </c>
+      <c r="L8" s="8">
+        <f ca="1">L$7*K8</f>
+        <v>2</v>
+      </c>
+      <c r="M8" s="9">
+        <f ca="1">SUM(F8,D8,H8,J8,L8)</f>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B9" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="4">
+        <f t="shared" ref="C9:C12" ca="1" si="0">RANDBETWEEN(1, 5)</f>
+        <v>4</v>
+      </c>
+      <c r="D9" s="4">
+        <f t="shared" ref="D9:D12" ca="1" si="1">D$7*C9</f>
+        <v>12</v>
+      </c>
+      <c r="E9" s="5">
+        <f t="shared" ref="E9:E12" ca="1" si="2">RANDBETWEEN(1, 5)</f>
+        <v>1</v>
+      </c>
+      <c r="F9" s="5">
+        <f t="shared" ref="F9:F12" ca="1" si="3">F$7*E9</f>
+        <v>5</v>
+      </c>
+      <c r="G9" s="6">
+        <f t="shared" ref="G9:G12" ca="1" si="4">RANDBETWEEN(1, 5)</f>
+        <v>3</v>
+      </c>
+      <c r="H9" s="6">
+        <f t="shared" ref="H9:H12" ca="1" si="5">H$7*G9</f>
+        <v>12</v>
+      </c>
+      <c r="I9" s="7">
+        <f t="shared" ref="I9:I12" ca="1" si="6">RANDBETWEEN(1, 5)</f>
+        <v>1</v>
+      </c>
+      <c r="J9" s="7">
+        <f t="shared" ref="J9:J12" ca="1" si="7">J$7*I9</f>
+        <v>3</v>
+      </c>
+      <c r="K9" s="8">
+        <f t="shared" ref="K9:L12" ca="1" si="8">RANDBETWEEN(1, 5)</f>
+        <v>4</v>
+      </c>
+      <c r="L9" s="8">
+        <f t="shared" ref="L9:L12" ca="1" si="9">L$7*K9</f>
+        <v>4</v>
+      </c>
+      <c r="M9" s="9">
+        <f ca="1">SUM(F9,D9,H9,J9,L9)</f>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B10" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="4">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="D10" s="4">
+        <f t="shared" ca="1" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="E10" s="5">
+        <f t="shared" ca="1" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="F10" s="5">
+        <f t="shared" ca="1" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="G10" s="6">
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="H10" s="6">
+        <f t="shared" ca="1" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="I10" s="7">
+        <f t="shared" ca="1" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="J10" s="7">
+        <f t="shared" ca="1" si="7"/>
+        <v>9</v>
+      </c>
+      <c r="K10" s="8">
+        <f t="shared" ca="1" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="L10" s="8">
+        <f t="shared" ca="1" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="M10" s="9">
+        <f t="shared" ref="M9:M12" ca="1" si="10">SUM(F10,D10,H10,J10,L10)</f>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B11" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="4">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="D11" s="4">
+        <f t="shared" ca="1" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="E11" s="5">
+        <f t="shared" ca="1" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="F11" s="5">
+        <f t="shared" ca="1" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="G11" s="6">
+        <f t="shared" ca="1" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="H11" s="6">
+        <f t="shared" ca="1" si="5"/>
+        <v>16</v>
+      </c>
+      <c r="I11" s="7">
+        <f t="shared" ca="1" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="J11" s="7">
+        <f t="shared" ca="1" si="7"/>
+        <v>6</v>
+      </c>
+      <c r="K11" s="8">
+        <f t="shared" ca="1" si="8"/>
+        <v>3</v>
+      </c>
+      <c r="L11" s="8">
+        <f t="shared" ca="1" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="M11" s="9">
+        <f ca="1">SUM(F11,D11,H11,J11,L11)</f>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B12" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="4">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="D12" s="4">
+        <f t="shared" ca="1" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="E12" s="5">
+        <f t="shared" ca="1" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F12" s="5">
+        <f t="shared" ca="1" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="G12" s="6">
+        <f t="shared" ca="1" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="H12" s="6">
+        <f t="shared" ca="1" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="I12" s="7">
+        <f t="shared" ca="1" si="6"/>
+        <v>5</v>
+      </c>
+      <c r="J12" s="7">
+        <f t="shared" ca="1" si="7"/>
+        <v>15</v>
+      </c>
+      <c r="K12" s="8">
+        <f t="shared" ca="1" si="8"/>
+        <v>2</v>
+      </c>
+      <c r="L12" s="8">
+        <f t="shared" ca="1" si="9"/>
+        <v>2</v>
+      </c>
+      <c r="M12" s="9">
+        <f ca="1">SUM(F12,D12,H12,J12,L12)</f>
+        <v>51</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <conditionalFormatting sqref="M8:M12">
+    <cfRule type="top10" dxfId="0" priority="1" percent="1" rank="10"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>